--- a/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>SNAL</t>
   </si>
@@ -656,211 +656,236 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>28600</v>
+      </c>
+      <c r="F8" s="3">
         <v>9000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>9900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>13500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>15300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>15600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>15500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>28100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>23500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>31200</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>18600</v>
+      </c>
+      <c r="F9" s="3">
         <v>9500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>9300</v>
       </c>
-      <c r="F9" s="3">
-        <v>9800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>11800</v>
-      </c>
       <c r="H9" s="3">
+        <v>20700</v>
+      </c>
+      <c r="I9" s="3">
+        <v>24500</v>
+      </c>
+      <c r="J9" s="3">
         <v>12400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>12300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>14900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>15300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>17200</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F10" s="3">
         <v>-500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>600</v>
       </c>
-      <c r="F10" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>3500</v>
-      </c>
       <c r="H10" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="J10" s="3">
         <v>3200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>3200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>13200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>8200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>14000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -877,31 +902,33 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1300</v>
+        <v>1800</v>
       </c>
       <c r="E12" s="3">
         <v>1200</v>
       </c>
       <c r="F12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H12" s="3">
         <v>1400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>2500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>200</v>
-      </c>
-      <c r="J12" s="3">
-        <v>200</v>
       </c>
       <c r="K12" s="3">
         <v>200</v>
@@ -909,11 +936,11 @@
       <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
+      <c r="M12" s="3">
+        <v>200</v>
+      </c>
+      <c r="N12" s="3">
+        <v>200</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
@@ -921,8 +948,14 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,8 +998,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -979,27 +1018,27 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>16300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,8 +1048,14 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1033,19 +1078,19 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>200</v>
+      </c>
+      <c r="N15" s="3">
+        <v>200</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
@@ -1053,8 +1098,14 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1068,96 +1119,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>24900</v>
+      </c>
+      <c r="F17" s="3">
         <v>14600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>14800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>17000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>20600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>17300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>17000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>21000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>35500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>22300</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-4900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-3500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-5300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>7100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-12000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>8900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1174,85 +1239,93 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-4400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-2700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>9700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-7200</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1262,8 +1335,14 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1271,10 +1350,10 @@
         <v>400</v>
       </c>
       <c r="E22" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="F22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G22" s="3">
         <v>300</v>
@@ -1283,119 +1362,137 @@
         <v>300</v>
       </c>
       <c r="I22" s="3">
+        <v>300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>300</v>
+      </c>
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-5500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>7300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-11600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>8900</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>600</v>
+      </c>
+      <c r="F24" s="3">
         <v>-1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-3200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1700</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1438,96 +1535,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-2300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>5800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-9100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>7300</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-4400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-4100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>5800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-9100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>7500</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1570,8 +1685,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1735,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1658,8 +1785,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1702,96 +1835,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-4400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-4100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>5800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-9100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>7500</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1834,101 +1985,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-4400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-4100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>5800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-9100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>7500</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1945,8 +2114,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1963,35 +2134,37 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F41" s="3">
         <v>4900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>12900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>14700</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2007,8 +2180,14 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2051,35 +2230,41 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>25200</v>
+      </c>
+      <c r="F43" s="3">
         <v>17300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>18700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>18400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>18200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>16900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>18600</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,8 +2280,14 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2139,35 +2330,41 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>16200</v>
+      </c>
+      <c r="F45" s="3">
         <v>13500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>13900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>14700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>11600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>13200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>11500</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2183,35 +2380,41 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>56700</v>
+      </c>
+      <c r="F46" s="3">
         <v>35800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>35500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>37200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>42600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>39200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>44700</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2227,31 +2430,37 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>7500</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2271,35 +2480,41 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F48" s="3">
         <v>7500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>8300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>8700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>9100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>9500</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2315,35 +2530,41 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>300</v>
+      </c>
+      <c r="F49" s="3">
         <v>400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>5400</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2359,8 +2580,14 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2403,8 +2630,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2447,35 +2680,41 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>19300</v>
+      </c>
+      <c r="F52" s="3">
         <v>17800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>16400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>19800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>19800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>21300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>21300</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2491,8 +2730,14 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2535,35 +2780,41 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>90900</v>
+      </c>
+      <c r="F54" s="3">
         <v>61400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>60400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>66200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>72800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>73100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>80900</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2579,8 +2830,14 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2597,8 +2854,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2615,35 +2874,37 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>35200</v>
+      </c>
+      <c r="F57" s="3">
         <v>29600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>28300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>27700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>29400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>29100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>28700</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2659,35 +2920,41 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>11900</v>
+      </c>
+      <c r="F58" s="3">
         <v>13700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>11800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>13200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>14500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>15700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>17300</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2703,35 +2970,41 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>24200</v>
+      </c>
+      <c r="F59" s="3">
         <v>10200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>8800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>8400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>7700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>8200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>13300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2747,35 +3020,41 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>71300</v>
+      </c>
+      <c r="F60" s="3">
         <v>53500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>48800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>49300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>51600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>53000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>59300</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,8 +3070,14 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2803,22 +3088,22 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>2800</v>
       </c>
       <c r="I61" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J61" s="3">
         <v>2800</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -2835,35 +3120,41 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7800</v>
+        <v>18400</v>
       </c>
       <c r="E62" s="3">
-        <v>7200</v>
+        <v>16700</v>
       </c>
       <c r="F62" s="3">
         <v>7800</v>
       </c>
       <c r="G62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="H62" s="3">
+        <v>7800</v>
+      </c>
+      <c r="I62" s="3">
         <v>8600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>12800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>12800</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2879,8 +3170,14 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2923,8 +3220,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2967,8 +3270,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3011,35 +3320,41 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>82600</v>
+      </c>
+      <c r="F66" s="3">
         <v>55800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>50500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>54500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>57900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>63200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>69400</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3055,8 +3370,14 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3073,8 +3394,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3117,8 +3440,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3161,8 +3490,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3205,8 +3540,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3249,35 +3590,41 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-16300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-11900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-7800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-4900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-2600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-1100</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3293,8 +3640,14 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3337,8 +3690,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3381,8 +3740,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3425,8 +3790,14 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -3434,26 +3805,26 @@
         <v>5600</v>
       </c>
       <c r="E76" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F76" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G76" s="3">
         <v>9800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>14900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>9900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>11500</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3840,14 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3513,101 +3890,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-4400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-4100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>5800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-9100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>7500</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3624,25 +4019,27 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>200</v>
+      </c>
+      <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>2000</v>
       </c>
       <c r="I83" s="3">
         <v>2000</v>
@@ -3651,14 +4048,14 @@
         <v>2000</v>
       </c>
       <c r="K83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M83" s="3">
         <v>4100</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3668,8 +4065,14 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3712,8 +4115,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3756,8 +4165,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3800,8 +4215,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3844,8 +4265,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3888,41 +4315,47 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>11300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-6700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-4100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>5000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2800</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,8 +4365,14 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3950,8 +4389,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3994,8 +4435,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4038,8 +4485,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4082,16 +4535,22 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
         <v>0</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -4100,23 +4559,23 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>1500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-6300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4126,8 +4585,14 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4144,8 +4609,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4188,8 +4655,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4232,8 +4705,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4276,8 +4755,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4320,40 +4805,46 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F100" s="3">
         <v>3900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-4300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>6500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-9400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>9100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
@@ -4364,8 +4855,14 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4391,14 +4888,14 @@
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4408,41 +4905,47 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F102" s="3">
         <v>2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-6400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-8700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>3800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-5600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-11000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>15500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-9500</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4450,6 +4953,12 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
   <si>
     <t>SNAL</t>
   </si>
@@ -656,75 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -734,47 +735,50 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E8" s="3">
         <v>14100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>28100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>23500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>31200</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -784,47 +788,50 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E9" s="3">
         <v>12000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>20700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>24500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>14900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -834,47 +841,50 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E10" s="3">
         <v>2100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-7200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-9200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>3200</v>
       </c>
       <c r="K10" s="3">
         <v>3200</v>
       </c>
       <c r="L10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M10" s="3">
         <v>13200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -884,8 +894,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,34 +917,35 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E12" s="3">
         <v>1800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>200</v>
       </c>
       <c r="L12" s="3">
         <v>200</v>
@@ -942,8 +956,8 @@
       <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
+      <c r="O12" s="3">
+        <v>200</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
@@ -954,8 +968,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,8 +1021,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1024,11 +1044,11 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1036,12 +1056,12 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>16300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,8 +1074,11 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1084,7 +1107,7 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>200</v>
@@ -1092,8 +1115,8 @@
       <c r="N15" s="3">
         <v>200</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>200</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
@@ -1104,8 +1127,11 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,47 +1147,48 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E17" s="3">
         <v>16300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>35500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22300</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1171,47 +1198,50 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-5600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-12000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8900</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1221,8 +1251,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,47 +1274,48 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
       </c>
       <c r="K20" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>400</v>
       </c>
       <c r="M20" s="3">
+        <v>400</v>
+      </c>
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1291,44 +1325,47 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1341,22 +1378,25 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
         <v>400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>400</v>
-      </c>
-      <c r="G22" s="3">
-        <v>300</v>
       </c>
       <c r="H22" s="3">
         <v>300</v>
@@ -1368,19 +1408,19 @@
         <v>300</v>
       </c>
       <c r="K22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L22" s="3">
         <v>200</v>
       </c>
       <c r="M22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
@@ -1391,47 +1431,50 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8900</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1441,47 +1484,50 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1700</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1491,8 +1537,11 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,47 +1590,50 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7300</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1591,47 +1643,50 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7500</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1641,8 +1696,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1802,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,47 +1908,50 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
       </c>
       <c r="K32" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-400</v>
       </c>
       <c r="M32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1891,47 +1961,50 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7500</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1941,8 +2014,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,47 +2067,50 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7500</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2041,52 +2120,55 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2096,8 +2178,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,38 +2222,39 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E41" s="3">
         <v>16100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14700</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2186,8 +2273,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2236,38 +2326,41 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E43" s="3">
         <v>11900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>17300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>18700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>18400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>16900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18600</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,8 +2379,11 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2336,38 +2432,41 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E45" s="3">
         <v>14400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11500</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2386,38 +2485,41 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E46" s="3">
         <v>42300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>56700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>42600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>39200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>44700</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,20 +2538,23 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E47" s="3">
         <v>6000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7500</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2462,8 +2567,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2486,38 +2591,41 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E48" s="3">
         <v>6700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>9100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9500</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2536,8 +2644,11 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2548,26 +2659,26 @@
         <v>300</v>
       </c>
       <c r="F49" s="3">
+        <v>300</v>
+      </c>
+      <c r="G49" s="3">
         <v>400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5400</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2586,8 +2697,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,37 +2803,40 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E52" s="3">
         <v>22900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>19800</v>
       </c>
       <c r="I52" s="3">
         <v>19800</v>
       </c>
       <c r="J52" s="3">
-        <v>21300</v>
+        <v>19800</v>
       </c>
       <c r="K52" s="3">
         <v>21300</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="L52" s="3">
+        <v>21300</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
@@ -2736,8 +2856,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,38 +2909,41 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E54" s="3">
         <v>78300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>90900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>61400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>60400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>66200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>72800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>73100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>80900</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,8 +2962,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,38 +3006,39 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E57" s="3">
         <v>26900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>35200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>29600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>28700</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,38 +3057,41 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E58" s="3">
         <v>6500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>17300</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2976,38 +3110,41 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E59" s="3">
         <v>26400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>24200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13300</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,38 +3163,41 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E60" s="3">
         <v>59800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>71300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>48800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>49300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>51600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>53000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>59300</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3076,8 +3216,11 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3094,19 +3237,19 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>2800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3200</v>
-      </c>
-      <c r="J61" s="3">
-        <v>2800</v>
       </c>
       <c r="K61" s="3">
         <v>2800</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -3126,37 +3269,40 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E62" s="3">
         <v>18400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8600</v>
-      </c>
-      <c r="J62" s="3">
-        <v>12800</v>
       </c>
       <c r="K62" s="3">
         <v>12800</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3">
+        <v>12800</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -3176,8 +3322,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,38 +3481,41 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E66" s="3">
         <v>72700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>82600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>50500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>54500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>57900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>63200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>69400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3376,8 +3534,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,38 +3767,41 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-15700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-13900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-16300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-7800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-4900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,8 +3820,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,38 +3979,41 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E76" s="3">
         <v>5600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11500</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,8 +4032,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,52 +4085,55 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3951,47 +4143,50 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7500</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,8 +4196,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,8 +4219,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4030,19 +4229,19 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>800</v>
-      </c>
-      <c r="I83" s="3">
-        <v>2000</v>
       </c>
       <c r="J83" s="3">
         <v>2000</v>
@@ -4054,11 +4253,11 @@
         <v>2000</v>
       </c>
       <c r="M83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N83" s="3">
         <v>4100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4071,8 +4270,11 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,44 +4535,47 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200</v>
+      </c>
+      <c r="E89" s="3">
         <v>6800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2800</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4371,8 +4588,11 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,8 +4611,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4441,8 +4662,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,19 +4768,22 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
@@ -4565,20 +4795,20 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>1500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6300</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4591,8 +4821,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4661,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,43 +5054,46 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>9100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -4861,8 +5107,11 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4894,11 +5143,11 @@
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4911,44 +5160,47 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9500</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4959,6 +5211,9 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
   <si>
     <t>SNAL</t>
   </si>
@@ -656,79 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -738,50 +739,53 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E8" s="3">
         <v>21600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>28100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>23500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>31200</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -791,50 +795,53 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E9" s="3">
         <v>13500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9300</v>
       </c>
-      <c r="I9" s="3">
-        <v>20700</v>
-      </c>
       <c r="J9" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K9" s="3">
         <v>24500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>14900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17200</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,50 +851,53 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E10" s="3">
         <v>8100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2100</v>
       </c>
-      <c r="F10" s="3">
-        <v>10000</v>
-      </c>
       <c r="G10" s="3">
+        <v>9900</v>
+      </c>
+      <c r="H10" s="3">
         <v>-500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>600</v>
       </c>
-      <c r="I10" s="3">
-        <v>-7200</v>
-      </c>
       <c r="J10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K10" s="3">
         <v>-9200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>3200</v>
       </c>
       <c r="L10" s="3">
         <v>3200</v>
       </c>
       <c r="M10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="N10" s="3">
         <v>13200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>14000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -897,8 +907,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,37 +931,38 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E12" s="3">
         <v>1900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>100</v>
-      </c>
-      <c r="L12" s="3">
-        <v>200</v>
       </c>
       <c r="M12" s="3">
         <v>200</v>
@@ -959,8 +973,8 @@
       <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
+      <c r="P12" s="3">
+        <v>200</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
@@ -971,8 +985,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,8 +1041,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1038,8 +1058,8 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1047,11 +1067,11 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
@@ -1059,12 +1079,12 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>16300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1077,8 +1097,11 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1110,7 +1133,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>200</v>
@@ -1118,8 +1141,8 @@
       <c r="O15" s="3">
         <v>200</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>200</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
@@ -1130,8 +1153,11 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,50 +1174,51 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E17" s="3">
         <v>18900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>21000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>35500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22300</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1201,50 +1228,53 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>400</v>
+      </c>
+      <c r="E18" s="3">
         <v>2700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-5600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8900</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,8 +1284,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,50 +1308,51 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>400</v>
+        <v>-300</v>
       </c>
       <c r="F20" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="G20" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>400</v>
       </c>
       <c r="N20" s="3">
+        <v>400</v>
+      </c>
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1328,47 +1362,50 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3100</v>
+        <v>500</v>
       </c>
       <c r="E21" s="3">
-        <v>-1800</v>
+        <v>3000</v>
       </c>
       <c r="F21" s="3">
-        <v>3800</v>
+        <v>-1900</v>
       </c>
       <c r="G21" s="3">
-        <v>-4900</v>
+        <v>3700</v>
       </c>
       <c r="H21" s="3">
-        <v>-4400</v>
+        <v>-5200</v>
       </c>
       <c r="I21" s="3">
-        <v>-2700</v>
+        <v>-4800</v>
       </c>
       <c r="J21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-3200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7200</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,8 +1418,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1390,16 +1430,16 @@
         <v>100</v>
       </c>
       <c r="E22" s="3">
+        <v>100</v>
+      </c>
+      <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>400</v>
-      </c>
-      <c r="H22" s="3">
-        <v>300</v>
       </c>
       <c r="I22" s="3">
         <v>300</v>
@@ -1411,19 +1451,19 @@
         <v>300</v>
       </c>
       <c r="L22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M22" s="3">
         <v>200</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>100</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
@@ -1434,50 +1474,53 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>400</v>
+      </c>
+      <c r="E23" s="3">
         <v>2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8900</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1487,50 +1530,53 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1700</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,8 +1586,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,50 +1642,53 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>200</v>
+      </c>
+      <c r="E26" s="3">
         <v>2300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7300</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,50 +1698,53 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>200</v>
+      </c>
+      <c r="E27" s="3">
         <v>2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7500</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,8 +1754,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1810,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1866,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1922,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,50 +1978,53 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-400</v>
+        <v>300</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-400</v>
       </c>
       <c r="N32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1964,50 +2034,53 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>200</v>
+      </c>
+      <c r="E33" s="3">
         <v>2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7500</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,8 +2090,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,50 +2146,53 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>200</v>
+      </c>
+      <c r="E35" s="3">
         <v>2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7500</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,55 +2202,58 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2181,8 +2263,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2287,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,41 +2309,42 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E41" s="3">
         <v>15500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>16100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14700</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,8 +2363,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2329,41 +2419,44 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E43" s="3">
         <v>11800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25200</v>
       </c>
-      <c r="G43" s="3">
-        <v>17300</v>
-      </c>
       <c r="H43" s="3">
-        <v>18700</v>
+        <v>15800</v>
       </c>
       <c r="I43" s="3">
+        <v>16800</v>
+      </c>
+      <c r="J43" s="3">
         <v>18400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>18200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18600</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2382,31 +2475,34 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2435,41 +2531,44 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>14300</v>
+        <v>300</v>
       </c>
       <c r="E45" s="3">
-        <v>14400</v>
+        <v>400</v>
       </c>
       <c r="F45" s="3">
-        <v>16200</v>
+        <v>500</v>
       </c>
       <c r="G45" s="3">
-        <v>13500</v>
+        <v>10100</v>
       </c>
       <c r="H45" s="3">
-        <v>13900</v>
+        <v>11400</v>
       </c>
       <c r="I45" s="3">
-        <v>14700</v>
+        <v>12100</v>
       </c>
       <c r="J45" s="3">
+        <v>11100</v>
+      </c>
+      <c r="K45" s="3">
         <v>11600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11500</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,41 +2587,44 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E46" s="3">
         <v>41600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>42300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>56700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>35500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>42600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>39200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>44700</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2541,19 +2643,22 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>4500</v>
-      </c>
-      <c r="E47" s="3">
-        <v>6000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>7500</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -2570,8 +2675,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2594,41 +2699,44 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>9100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>9500</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,8 +2755,11 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2662,26 +2773,26 @@
         <v>300</v>
       </c>
       <c r="G49" s="3">
+        <v>300</v>
+      </c>
+      <c r="H49" s="3">
         <v>400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5400</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,8 +2811,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2867,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,40 +2923,43 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>22700</v>
+        <v>10300</v>
       </c>
       <c r="E52" s="3">
-        <v>22900</v>
+        <v>12500</v>
       </c>
       <c r="F52" s="3">
-        <v>19300</v>
+        <v>12100</v>
       </c>
       <c r="G52" s="3">
-        <v>17800</v>
+        <v>16600</v>
       </c>
       <c r="H52" s="3">
-        <v>16400</v>
+        <v>6900</v>
       </c>
       <c r="I52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J52" s="3">
+        <v>12200</v>
+      </c>
+      <c r="K52" s="3">
         <v>19800</v>
-      </c>
-      <c r="J52" s="3">
-        <v>19800</v>
-      </c>
-      <c r="K52" s="3">
-        <v>21300</v>
       </c>
       <c r="L52" s="3">
         <v>21300</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>21300</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -2859,8 +2979,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,41 +3035,44 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E54" s="3">
         <v>75400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>78300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>90900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>61400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>60400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>66200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>72800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>73100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>80900</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3091,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3115,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,41 +3137,42 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E57" s="3">
         <v>21800</v>
       </c>
-      <c r="E57" s="3">
-        <v>26900</v>
-      </c>
       <c r="F57" s="3">
-        <v>35200</v>
+        <v>9900</v>
       </c>
       <c r="G57" s="3">
-        <v>29600</v>
+        <v>12100</v>
       </c>
       <c r="H57" s="3">
-        <v>28300</v>
+        <v>10000</v>
       </c>
       <c r="I57" s="3">
-        <v>27700</v>
+        <v>8700</v>
       </c>
       <c r="J57" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K57" s="3">
         <v>29400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>29100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>28700</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3060,41 +3191,44 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5800</v>
+        <v>7400</v>
       </c>
       <c r="E58" s="3">
-        <v>6500</v>
+        <v>7300</v>
       </c>
       <c r="F58" s="3">
-        <v>11900</v>
+        <v>8000</v>
       </c>
       <c r="G58" s="3">
-        <v>13700</v>
+        <v>13400</v>
       </c>
       <c r="H58" s="3">
-        <v>11800</v>
+        <v>15200</v>
       </c>
       <c r="I58" s="3">
         <v>13200</v>
       </c>
       <c r="J58" s="3">
+        <v>14700</v>
+      </c>
+      <c r="K58" s="3">
         <v>14500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>17300</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3113,41 +3247,44 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25700</v>
+        <v>13300</v>
       </c>
       <c r="E59" s="3">
-        <v>26400</v>
+        <v>21500</v>
       </c>
       <c r="F59" s="3">
-        <v>24200</v>
+        <v>38900</v>
       </c>
       <c r="G59" s="3">
-        <v>10200</v>
+        <v>42300</v>
       </c>
       <c r="H59" s="3">
-        <v>8800</v>
+        <v>25500</v>
       </c>
       <c r="I59" s="3">
-        <v>8400</v>
+        <v>23700</v>
       </c>
       <c r="J59" s="3">
+        <v>24100</v>
+      </c>
+      <c r="K59" s="3">
         <v>7700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3166,41 +3303,44 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E60" s="3">
         <v>53300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>59800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>71300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>53500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>48800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>49300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>53000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>59300</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,40 +3359,43 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="I61" s="3">
-        <v>2800</v>
+        <v>2200</v>
       </c>
       <c r="J61" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K61" s="3">
         <v>3200</v>
-      </c>
-      <c r="K61" s="3">
-        <v>2800</v>
       </c>
       <c r="L61" s="3">
         <v>2800</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -3272,40 +3415,43 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>19700</v>
+        <v>300</v>
       </c>
       <c r="E62" s="3">
-        <v>18400</v>
+        <v>300</v>
       </c>
       <c r="F62" s="3">
-        <v>16700</v>
+        <v>300</v>
       </c>
       <c r="G62" s="3">
-        <v>7800</v>
+        <v>300</v>
       </c>
       <c r="H62" s="3">
-        <v>7200</v>
+        <v>300</v>
       </c>
       <c r="I62" s="3">
-        <v>7800</v>
+        <v>400</v>
       </c>
       <c r="J62" s="3">
+        <v>400</v>
+      </c>
+      <c r="K62" s="3">
         <v>8600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>12800</v>
       </c>
       <c r="L62" s="3">
         <v>12800</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>12800</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -3325,8 +3471,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3527,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3583,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,41 +3639,44 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>67500</v>
+        <v>64100</v>
       </c>
       <c r="E66" s="3">
-        <v>72700</v>
+        <v>73000</v>
       </c>
       <c r="F66" s="3">
-        <v>82600</v>
+        <v>78200</v>
       </c>
       <c r="G66" s="3">
-        <v>55800</v>
+        <v>88100</v>
       </c>
       <c r="H66" s="3">
-        <v>50500</v>
+        <v>61300</v>
       </c>
       <c r="I66" s="3">
-        <v>54500</v>
+        <v>56000</v>
       </c>
       <c r="J66" s="3">
+        <v>60000</v>
+      </c>
+      <c r="K66" s="3">
         <v>57900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>63200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>69400</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3695,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3719,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3773,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3829,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +3885,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,41 +3941,44 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-15700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-13900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-16300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-11900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-7800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-4900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1100</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3823,8 +3997,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4053,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4109,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,41 +4165,44 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E76" s="3">
         <v>7900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11500</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4035,8 +4221,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,55 +4277,58 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4146,50 +4338,53 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>200</v>
+      </c>
+      <c r="E81" s="3">
         <v>2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7500</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4199,8 +4394,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,8 +4418,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4232,19 +4431,19 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
         <v>200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>2000</v>
       </c>
       <c r="K83" s="3">
         <v>2000</v>
@@ -4256,11 +4455,11 @@
         <v>2000</v>
       </c>
       <c r="N83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O83" s="3">
         <v>4100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4273,8 +4472,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4528,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4584,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4640,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4696,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,47 +4752,50 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E89" s="3">
         <v>200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4591,8 +4808,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,31 +4832,32 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4665,8 +4886,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4942,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,47 +4998,50 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>1500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6300</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4824,8 +5054,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,31 +5078,32 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4898,8 +5132,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5188,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5244,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,46 +5300,49 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
@@ -5110,8 +5356,11 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5146,11 +5395,11 @@
         <v>0</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5163,47 +5412,50 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-11000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9500</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5214,6 +5466,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
   <si>
     <t>SNAL</t>
   </si>
@@ -656,262 +656,287 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>26200</v>
+      </c>
+      <c r="F8" s="3">
         <v>22500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>21600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>14100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>28600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>9000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>9900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>13500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>15300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>15600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>15500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>28100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>23500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>31200</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F9" s="3">
         <v>13800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>13500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>12000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>18600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>9500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>9300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>10900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>24500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>12400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>12300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>14900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>15300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>17200</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>11300</v>
+      </c>
+      <c r="F10" s="3">
         <v>8700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>8100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>9900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-9200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>3200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>13200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>8200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>14000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,43 +957,45 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F12" s="3">
         <v>3900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1800</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1300</v>
       </c>
       <c r="I12" s="3">
         <v>1200</v>
       </c>
       <c r="J12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L12" s="3">
         <v>1400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>200</v>
-      </c>
-      <c r="N12" s="3">
-        <v>200</v>
       </c>
       <c r="O12" s="3">
         <v>200</v>
@@ -976,11 +1003,11 @@
       <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
+      <c r="Q12" s="3">
+        <v>200</v>
+      </c>
+      <c r="R12" s="3">
+        <v>200</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
@@ -988,8 +1015,14 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,8 +1077,14 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1058,39 +1097,39 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>16300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1100,8 +1139,14 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1136,19 +1181,19 @@
         <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
+      <c r="Q15" s="3">
+        <v>200</v>
+      </c>
+      <c r="R15" s="3">
+        <v>200</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
@@ -1156,8 +1201,14 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,120 +1226,134 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>23200</v>
+      </c>
+      <c r="F17" s="3">
         <v>22100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>18900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>16300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>24900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>14600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>14800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>17000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>20600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>17300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>17000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>21000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>35500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>22300</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F18" s="3">
         <v>400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>2700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-5600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-4900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-5300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>7100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-12000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>8900</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,109 +1374,117 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="E20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F21" s="3">
         <v>500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>3700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-5200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-4800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>1000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>9700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-7200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1421,8 +1494,14 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1433,19 +1512,19 @@
         <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
         <v>400</v>
       </c>
       <c r="I22" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="J22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K22" s="3">
         <v>300</v>
@@ -1454,143 +1533,161 @@
         <v>300</v>
       </c>
       <c r="M22" s="3">
+        <v>300</v>
+      </c>
+      <c r="N22" s="3">
+        <v>300</v>
+      </c>
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F23" s="3">
         <v>400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>3000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-5600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-5200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-5500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>7300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-11600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>8900</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
-      </c>
-      <c r="E24" s="3">
-        <v>600</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-500</v>
       </c>
       <c r="G24" s="3">
         <v>600</v>
       </c>
       <c r="H24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I24" s="3">
+        <v>600</v>
+      </c>
+      <c r="J24" s="3">
         <v>-1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-3200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>1700</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,120 +1742,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F26" s="3">
         <v>200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>5800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-9100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>7300</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F27" s="3">
         <v>200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>2400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>5800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-9100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>7500</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1928,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1869,8 +1990,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +2052,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,120 +2114,138 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F33" s="3">
         <v>200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>5800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-9100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>7500</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,125 +2300,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F35" s="3">
         <v>200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>5800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-9100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>7500</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2457,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,47 +2481,49 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F41" s="3">
         <v>10600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>15500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>16100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>15200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>12900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>9000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>14700</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,8 +2539,14 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2422,8 +2601,14 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2431,38 +2616,38 @@
         <v>10800</v>
       </c>
       <c r="E43" s="3">
+        <v>12800</v>
+      </c>
+      <c r="F43" s="3">
+        <v>10800</v>
+      </c>
+      <c r="G43" s="3">
         <v>11800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>11900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>25200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>15800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>16800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>18400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>18200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>16900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>18600</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2478,8 +2663,14 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2504,11 +2695,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2534,47 +2725,53 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>700</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
-        <v>10100</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>600</v>
+      </c>
+      <c r="J45" s="3">
         <v>11400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>12100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>11100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>11600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>13200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>11500</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2590,47 +2787,53 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>31200</v>
+      </c>
+      <c r="F46" s="3">
         <v>36500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>41600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>42300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>56700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>35800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>35500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>37200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>42600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>39200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>44700</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,8 +2849,14 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2678,11 +2887,11 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2702,47 +2911,53 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F48" s="3">
         <v>6000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>6400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>6700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>8300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>8700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>9100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>9500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2758,16 +2973,22 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>300</v>
+        <v>2200</v>
       </c>
       <c r="E49" s="3">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F49" s="3">
         <v>300</v>
@@ -2776,29 +2997,29 @@
         <v>300</v>
       </c>
       <c r="H49" s="3">
+        <v>300</v>
+      </c>
+      <c r="I49" s="3">
+        <v>300</v>
+      </c>
+      <c r="J49" s="3">
         <v>400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>5400</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,8 +3035,14 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +3097,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,47 +3159,53 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F52" s="3">
         <v>10300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>12500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>12100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>16600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>6900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>6900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>12200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>19800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>21300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>21300</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2982,8 +3221,14 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,47 +3283,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>64500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>62200</v>
+      </c>
+      <c r="F54" s="3">
         <v>66800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>75400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>78300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>90900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>61400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>60400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>66200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>72800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>73100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>80900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3094,8 +3345,14 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3373,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,47 +3397,49 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F57" s="3">
         <v>19600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>21800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>12100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>10000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>8700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>8100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>29400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>29100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>28700</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3194,47 +3455,53 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F58" s="3">
         <v>7400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>7300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>8000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>13400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>15200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>13200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>14700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>14500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>15700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>17300</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3250,47 +3517,53 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>19300</v>
+      </c>
+      <c r="F59" s="3">
         <v>13300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>21500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>38900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>42300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>25500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>23700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>24100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>7700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>8200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>13300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3306,47 +3579,53 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>36200</v>
+      </c>
+      <c r="F60" s="3">
         <v>43600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>53300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>59800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>71300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>53500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>48800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>49300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>51600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>53000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>59300</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3362,47 +3641,53 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>100</v>
+      </c>
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>5300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2800</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3418,8 +3703,14 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3439,26 +3730,26 @@
         <v>300</v>
       </c>
       <c r="I62" s="3">
+        <v>300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>300</v>
+      </c>
+      <c r="K62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>8600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>12800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>12800</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3765,14 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3827,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3889,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,47 +3951,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>58000</v>
+      </c>
+      <c r="F66" s="3">
         <v>64100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>73000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>78200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>88100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>61300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>56000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>60000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>57900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>63200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>69400</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3698,8 +4013,14 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +4041,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +4099,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +4161,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3888,8 +4223,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,47 +4285,53 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-13200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-13500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-15700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-13900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-16300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-11900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-7800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-4900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-2600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1100</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4000,8 +4347,14 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4409,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4471,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,47 +4533,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F76" s="3">
         <v>8200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>7900</v>
-      </c>
-      <c r="F76" s="3">
-        <v>5600</v>
-      </c>
-      <c r="G76" s="3">
-        <v>8300</v>
       </c>
       <c r="H76" s="3">
         <v>5600</v>
       </c>
       <c r="I76" s="3">
+        <v>8300</v>
+      </c>
+      <c r="J76" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K76" s="3">
         <v>9800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>14900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>11500</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4224,8 +4595,14 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,125 +4657,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F81" s="3">
         <v>200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>5800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-9100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>7500</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,8 +4814,10 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4443,13 +4840,13 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
-      </c>
-      <c r="K83" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>2000</v>
       </c>
       <c r="M83" s="3">
         <v>2000</v>
@@ -4458,14 +4855,14 @@
         <v>2000</v>
       </c>
       <c r="O83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>4100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4475,8 +4872,14 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4934,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4996,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +5058,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +5120,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,53 +5182,59 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>6800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>11300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-6700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>5000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4811,8 +5244,14 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,8 +5272,10 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4859,11 +5300,11 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4889,8 +5330,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5392,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,13 +5454,19 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-1900</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>3</v>
@@ -5027,27 +5486,27 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>1500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-6300</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5057,8 +5516,14 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,8 +5544,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5105,11 +5572,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5135,8 +5602,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5664,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5726,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,52 +5788,58 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="E100" s="3">
+        <v>200</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-5900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>3900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-4300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>6500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-9400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>9100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
@@ -5359,8 +5850,14 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5398,14 +5895,14 @@
         <v>0</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5415,53 +5912,59 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>10300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-6400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-8700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>3800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-5600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-11000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>15500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-9500</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,6 +5972,12 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>SNAL</t>
   </si>
@@ -656,90 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -749,59 +750,62 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E8" s="3">
         <v>20100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>26200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>28600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>28100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>23500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31200</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -811,59 +815,62 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E9" s="3">
         <v>14300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>14900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>24500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>17200</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,59 +880,62 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-9200</v>
-      </c>
-      <c r="N10" s="3">
-        <v>3200</v>
       </c>
       <c r="O10" s="3">
         <v>3200</v>
       </c>
       <c r="P10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Q10" s="3">
         <v>13200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>14000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,46 +972,47 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E12" s="3">
         <v>3600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>100</v>
-      </c>
-      <c r="O12" s="3">
-        <v>200</v>
       </c>
       <c r="P12" s="3">
         <v>200</v>
@@ -1009,8 +1023,8 @@
       <c r="R12" s="3">
         <v>200</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
+      <c r="S12" s="3">
+        <v>200</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
@@ -1021,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,13 +1100,16 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>400</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1103,11 +1123,11 @@
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1115,11 +1135,11 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
@@ -1127,12 +1147,12 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>16300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1145,8 +1165,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1187,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>200</v>
@@ -1195,8 +1218,8 @@
       <c r="R15" s="3">
         <v>200</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
+      <c r="S15" s="3">
+        <v>200</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,59 +1254,60 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E17" s="3">
         <v>24200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>23200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>22100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22300</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1290,59 +1317,62 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-12000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1382,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,59 +1409,60 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1500</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>400</v>
       </c>
       <c r="Q20" s="3">
+        <v>400</v>
+      </c>
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,56 +1472,59 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7200</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,13 +1537,16 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -1518,16 +1558,16 @@
         <v>100</v>
       </c>
       <c r="H22" s="3">
+        <v>100</v>
+      </c>
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>300</v>
       </c>
       <c r="L22" s="3">
         <v>300</v>
@@ -1539,19 +1579,19 @@
         <v>300</v>
       </c>
       <c r="O22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P22" s="3">
         <v>200</v>
       </c>
       <c r="Q22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>100</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1562,59 +1602,62 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-11600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1624,59 +1667,62 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1700</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1686,8 +1732,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,59 +1797,62 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7300</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1810,59 +1862,62 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7500</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1872,8 +1927,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,59 +2187,62 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1500</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-400</v>
       </c>
       <c r="Q32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,59 +2252,62 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7500</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2244,8 +2317,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,59 +2382,62 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7500</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,64 +2447,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2435,8 +2517,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,50 +2569,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E41" s="3">
         <v>9400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14700</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2632,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2607,50 +2697,53 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E43" s="3">
         <v>10800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>25200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>16800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>18600</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2669,8 +2762,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2701,8 +2797,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2731,50 +2827,53 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11500</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,50 +2892,53 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E46" s="3">
         <v>31100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>31200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>36500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>41600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>42300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>56700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>35800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>35500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>37200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>42600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>44700</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,8 +2957,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2893,8 +2998,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2917,50 +3022,53 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E48" s="3">
         <v>5300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9500</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,19 +3087,22 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>300</v>
       </c>
       <c r="G49" s="3">
         <v>300</v>
@@ -3003,26 +3114,26 @@
         <v>300</v>
       </c>
       <c r="J49" s="3">
+        <v>300</v>
+      </c>
+      <c r="K49" s="3">
         <v>400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5400</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,49 +3282,52 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E52" s="3">
         <v>13100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>6900</v>
       </c>
       <c r="K52" s="3">
         <v>6900</v>
       </c>
       <c r="L52" s="3">
+        <v>6900</v>
+      </c>
+      <c r="M52" s="3">
         <v>12200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>19800</v>
-      </c>
-      <c r="N52" s="3">
-        <v>21300</v>
       </c>
       <c r="O52" s="3">
         <v>21300</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>21300</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,50 +3412,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E54" s="3">
         <v>64500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>62200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>66800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>75400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>90900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>61400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>60400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>66200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>72800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>73100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>80900</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,50 +3529,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E57" s="3">
         <v>4200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>29400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>29100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>28700</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,50 +3592,53 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E58" s="3">
         <v>9600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>17300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,50 +3657,53 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E59" s="3">
         <v>19600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>38900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>42300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,50 +3722,53 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>55200</v>
+      </c>
+      <c r="E60" s="3">
         <v>36800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>43600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>53300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>59800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>71300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>53500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>48800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>49300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>51600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>53000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>59300</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3787,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3659,37 +3802,37 @@
         <v>100</v>
       </c>
       <c r="F61" s="3">
+        <v>100</v>
+      </c>
+      <c r="G61" s="3">
         <v>300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3200</v>
-      </c>
-      <c r="N61" s="3">
-        <v>2800</v>
       </c>
       <c r="O61" s="3">
         <v>2800</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -3709,8 +3852,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3736,22 +3882,22 @@
         <v>300</v>
       </c>
       <c r="K62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L62" s="3">
         <v>400</v>
       </c>
       <c r="M62" s="3">
+        <v>400</v>
+      </c>
+      <c r="N62" s="3">
         <v>8600</v>
-      </c>
-      <c r="N62" s="3">
-        <v>12800</v>
       </c>
       <c r="O62" s="3">
         <v>12800</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
+      <c r="P62" s="3">
+        <v>12800</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,50 +4112,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E66" s="3">
         <v>60900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>58000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>64100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>73000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>78200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>88100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>61300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>56000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>60000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>57900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>63200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>69400</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,50 +4462,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-14100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-12100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-13200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-15700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-13900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-16300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1100</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,50 +4722,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11500</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,64 +4852,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4730,59 +4922,62 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7500</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4792,8 +4987,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,8 +5014,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4846,10 +5045,10 @@
         <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
-      </c>
-      <c r="M83" s="3">
-        <v>2000</v>
       </c>
       <c r="N83" s="3">
         <v>2000</v>
@@ -4861,11 +5060,11 @@
         <v>2000</v>
       </c>
       <c r="Q83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R83" s="3">
         <v>4100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4878,8 +5077,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,56 +5402,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E89" s="3">
         <v>800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2800</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5250,8 +5467,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,8 +5494,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5306,8 +5527,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -5336,8 +5557,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,17 +5687,20 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5492,24 +5722,24 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>1500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6300</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5522,8 +5752,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5578,8 +5812,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,55 +6037,58 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E100" s="3">
         <v>3100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
@@ -5856,8 +6102,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5901,11 +6150,11 @@
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5918,56 +6167,59 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9500</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,6 +6230,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
   <si>
     <t>SNAL</t>
   </si>
@@ -656,313 +656,338 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>25100</v>
+      </c>
+      <c r="F8" s="3">
         <v>13800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>22200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>20100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>26200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>22500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>21600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>14100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>28600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>9000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>9900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>13500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>15300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>15600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>15500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>28100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>23500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>31200</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F9" s="3">
         <v>13800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>15200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>14300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>14900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>13800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>13500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>12000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>18600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>9500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>9300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>10900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>24500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>12400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>12300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>14900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>15300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>17200</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>11700</v>
       </c>
       <c r="E10" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
         <v>7000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>5800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>11300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>8700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>8100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>9900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-9200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>3200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>3200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>13200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>8200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>14000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,55 +1012,57 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F12" s="3">
         <v>3700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>3300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>3600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>4100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>3900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1800</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1300</v>
       </c>
       <c r="M12" s="3">
         <v>1200</v>
       </c>
       <c r="N12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P12" s="3">
         <v>1400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>100</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>200</v>
-      </c>
-      <c r="R12" s="3">
-        <v>200</v>
       </c>
       <c r="S12" s="3">
         <v>200</v>
@@ -1043,11 +1070,11 @@
       <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
+      <c r="U12" s="3">
+        <v>200</v>
+      </c>
+      <c r="V12" s="3">
+        <v>200</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
@@ -1055,8 +1082,14 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,23 +1156,29 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>800</v>
+      </c>
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1149,39 +1188,39 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
         <v>16300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1191,16 +1230,22 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1239,19 +1284,19 @@
         <v>100</v>
       </c>
       <c r="R15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T15" s="3">
         <v>200</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
+      <c r="U15" s="3">
+        <v>200</v>
+      </c>
+      <c r="V15" s="3">
+        <v>200</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
@@ -1259,8 +1304,14 @@
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,144 +1333,158 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>25800</v>
+      </c>
+      <c r="F17" s="3">
         <v>23300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>23600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>24200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>23200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>22100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>18900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>16300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>24900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>14600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>14800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>17000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>20600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>17300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>17000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>21000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>35500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>22300</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-9500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>2700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-5600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-4900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>7100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-12000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>8900</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,133 +1509,141 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1500</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-9300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-2100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-3300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>3000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>3700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-5200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-3400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-3200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>9700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-7200</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1653,14 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1592,10 +1671,10 @@
         <v>200</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H22" s="3">
         <v>100</v>
@@ -1604,19 +1683,19 @@
         <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>400</v>
       </c>
       <c r="M22" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="N22" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O22" s="3">
         <v>300</v>
@@ -1625,167 +1704,185 @@
         <v>300</v>
       </c>
       <c r="Q22" s="3">
+        <v>300</v>
+      </c>
+      <c r="R22" s="3">
+        <v>300</v>
+      </c>
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-9400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-3400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>2800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-5600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-5500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>7300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-11600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>8900</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>13900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-1500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
-      </c>
-      <c r="I24" s="3">
-        <v>600</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-500</v>
       </c>
       <c r="K24" s="3">
         <v>600</v>
       </c>
       <c r="L24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M24" s="3">
+        <v>600</v>
+      </c>
+      <c r="N24" s="3">
         <v>-1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-1100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-3200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-2400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1700</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1949,162 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-7900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-16600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-4400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>5800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-9100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>7300</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-7900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-16600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-4400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>5800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-9100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>7500</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2171,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2245,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2319,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,144 +2393,162 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1500</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-16600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-4400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>5800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-9100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>7500</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2615,167 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-16600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-4400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>5800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-9100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>7500</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2800,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,59 +2828,61 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F41" s="3">
         <v>12300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>10600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>15500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>16100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>15200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>12900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>9000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>14700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2725,8 +2898,14 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2793,59 +2972,65 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F43" s="3">
         <v>7800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>18000</v>
-      </c>
-      <c r="F43" s="3">
-        <v>10800</v>
-      </c>
-      <c r="G43" s="3">
-        <v>12800</v>
       </c>
       <c r="H43" s="3">
         <v>10800</v>
       </c>
       <c r="I43" s="3">
+        <v>12800</v>
+      </c>
+      <c r="J43" s="3">
+        <v>10800</v>
+      </c>
+      <c r="K43" s="3">
         <v>11800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>11900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>25200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>15800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>16800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>18400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>18200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>16900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>18600</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2861,8 +3046,14 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2899,11 +3090,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2929,59 +3120,65 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>400</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E45" s="3">
         <v>400</v>
       </c>
       <c r="F45" s="3">
+        <v>400</v>
+      </c>
+      <c r="G45" s="3">
+        <v>400</v>
+      </c>
+      <c r="H45" s="3">
         <v>600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>11400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>12100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>11100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>11600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>13200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>11500</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,59 +3194,65 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>31100</v>
+      </c>
+      <c r="F46" s="3">
         <v>34700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>38800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>31100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>31200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>36500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>41600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>42300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>56700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>35800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>35500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>37200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>42600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>39200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>44700</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3065,8 +3268,14 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3109,11 +3318,11 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3133,59 +3342,65 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F48" s="3">
         <v>4600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>5300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>5700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>6000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>6400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>6700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>7100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>7500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>7900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>8300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>8700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>9100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>9500</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,28 +3416,34 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F49" s="3">
         <v>4400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>300</v>
-      </c>
-      <c r="I49" s="3">
-        <v>300</v>
       </c>
       <c r="J49" s="3">
         <v>300</v>
@@ -3231,29 +3452,29 @@
         <v>300</v>
       </c>
       <c r="L49" s="3">
+        <v>300</v>
+      </c>
+      <c r="M49" s="3">
+        <v>300</v>
+      </c>
+      <c r="N49" s="3">
         <v>400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>5400</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3269,8 +3490,14 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3564,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,59 +3638,65 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F52" s="3">
         <v>7400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>10700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>13100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>13500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>10300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>12500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>12100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>16600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>6900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>6900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>12200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>19800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>21300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>21300</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3712,14 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,59 +3786,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>59300</v>
+      </c>
+      <c r="F54" s="3">
         <v>51100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>58000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>64500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>62200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>66800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>75400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>78300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>90900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>61400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>60400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>66200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>72800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>73100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>80900</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,8 +3860,14 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3892,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,59 +3920,61 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F57" s="3">
         <v>4900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>19600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>21800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>9900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>12100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>10000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>8700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>8100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>29400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>29100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>28700</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3729,59 +3990,65 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F58" s="3">
         <v>10800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>12200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>9600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>7200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>7400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>7300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>8000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>13400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>15200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>13200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>14700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>14500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>15700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>17300</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3797,59 +4064,65 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>34900</v>
+      </c>
+      <c r="F59" s="3">
         <v>46000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>32700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>19600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>19300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>13300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>21500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>38900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>42300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>25500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>23700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>24100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>7700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>8200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>13300</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,59 +4138,65 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>49800</v>
+      </c>
+      <c r="F60" s="3">
         <v>65600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>55200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>36800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>36200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>43600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>53300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>59800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>71300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>53500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>48800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>49300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>51600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>53000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>59300</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,16 +4212,22 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>10700</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>13600</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
@@ -3951,41 +4236,41 @@
         <v>100</v>
       </c>
       <c r="H61" s="3">
+        <v>100</v>
+      </c>
+      <c r="I61" s="3">
+        <v>100</v>
+      </c>
+      <c r="J61" s="3">
         <v>300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>5300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2800</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4001,16 +4286,22 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E62" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F62" s="3">
         <v>300</v>
@@ -4034,26 +4325,26 @@
         <v>300</v>
       </c>
       <c r="M62" s="3">
+        <v>300</v>
+      </c>
+      <c r="N62" s="3">
+        <v>300</v>
+      </c>
+      <c r="O62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>8600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>12800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>12800</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4069,8 +4360,14 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4434,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4508,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,59 +4582,65 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>81200</v>
+      </c>
+      <c r="F66" s="3">
         <v>72100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>71400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>60900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>58000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>64100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>73000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>78200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>88100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>61300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>56000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>60000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>57900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>63200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>69400</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4341,8 +4656,14 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4688,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4758,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4832,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4571,8 +4906,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,59 +4980,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-37200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-38500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-30600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-14100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-12100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-13200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-13500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-15700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-13900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-16300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-11900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-7800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-4900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-1100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4707,8 +5054,14 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +5128,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5202,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,59 +5276,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="F76" s="3">
         <v>-15600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-8000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>9100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>9700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7900</v>
-      </c>
-      <c r="J76" s="3">
-        <v>5600</v>
-      </c>
-      <c r="K76" s="3">
-        <v>8300</v>
       </c>
       <c r="L76" s="3">
         <v>5600</v>
       </c>
       <c r="M76" s="3">
+        <v>8300</v>
+      </c>
+      <c r="N76" s="3">
+        <v>5600</v>
+      </c>
+      <c r="O76" s="3">
         <v>9800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>11800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>14900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>11500</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4979,8 +5350,14 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5424,167 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-16600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-4400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>5800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-9100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>7500</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,8 +5609,10 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5250,13 +5647,13 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
+        <v>100</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
-      </c>
-      <c r="O83" s="3">
-        <v>2000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>2000</v>
       </c>
       <c r="Q83" s="3">
         <v>2000</v>
@@ -5265,14 +5662,14 @@
         <v>2000</v>
       </c>
       <c r="S83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U83" s="3">
         <v>4100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5282,8 +5679,14 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5753,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5827,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5901,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5975,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,65 +6049,71 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F89" s="3">
         <v>6600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-3200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-5000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>6800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>11300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-6700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>5000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2800</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5690,8 +6123,14 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,19 +6155,21 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>3</v>
@@ -5754,11 +6195,11 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -5784,8 +6225,14 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6299,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,26 +6373,32 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1100</v>
+        <v>-200</v>
       </c>
       <c r="E94" s="3">
         <v>-1100</v>
       </c>
       <c r="F94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5958,27 +6417,27 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>1500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-6300</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5988,8 +6447,14 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6479,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6052,11 +6519,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6082,8 +6549,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6623,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6697,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,64 +6771,70 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>3100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-5900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>3900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-4300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-2000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>6500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-9400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>9100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
@@ -6354,20 +6845,26 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
@@ -6405,14 +6902,14 @@
         <v>0</v>
       </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6422,65 +6919,71 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F102" s="3">
         <v>4400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-4900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>10300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>2000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-6400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-8700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>3800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-11000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>15500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-9500</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6488,6 +6991,12 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
